--- a/naver-place-crawler/results_health/김포_헬스장.xlsx
+++ b/naver-place-crawler/results_health/김포_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,39 +559,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>인어스휘트니스 헬스 PT &amp; 필라테스 골프 김포점</t>
+          <t>라임 피트니스 PT 김포장기점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>inus-fitness09@naver.com</t>
+          <t>lime___fitness@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1312-8337</t>
+          <t>0507-1381-7494</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 김포시 김포한강4로 113 신한프라자 10층</t>
+          <t>경기 김포시 태장로 780 베네치아의 아침 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://inushnl.com/layout/fitness/home.php?go=main&amp;</t>
+          <t>https://blog.naver.com/lime___fitness</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -601,15 +601,19 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4hh9p</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1410</v>
+        <v>480</v>
       </c>
       <c r="Q2" t="n">
-        <v>782</v>
+        <v>488</v>
       </c>
       <c r="R2" t="n">
-        <v>2192</v>
+        <v>968</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1901435715</t>
+          <t>1802881557</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1901435715</t>
+          <t>https://m.place.naver.com/place/1802881557</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -653,39 +657,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>짐원휘트니스 구래2호점 헬스PT</t>
+          <t>포워드 휘트니스 감정점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>gymonelab@naver.com</t>
+          <t>forward-fitness2@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1438-9680</t>
+          <t>0507-1414-6704</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 김포시 김포한강8로 400 홍은프라자 4층</t>
+          <t>경기 김포시 중봉1로 17 4층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://gymone.kr</t>
+          <t>https://www.instagram.com/forward.fitness.02</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -695,18 +699,22 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w936str</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1023</v>
+        <v>340</v>
       </c>
       <c r="Q3" t="n">
-        <v>348</v>
+        <v>576</v>
       </c>
       <c r="R3" t="n">
-        <v>1371</v>
+        <v>916</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1143886551</t>
+          <t>1451785502</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1143886551</t>
+          <t>https://m.place.naver.com/place/1451785502</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -747,34 +755,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>브이짐 헬스&amp;PT 풍무점</t>
+          <t>비비짐 김포점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>lki666@naver.com</t>
+          <t>bbgymgimpo@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1433-9679</t>
+          <t>0507-1402-5223</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 김포시 풍무로 20 스타프라자</t>
+          <t>경기 김포시 사우중로 93 한빛프라자 7층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lki666</t>
+          <t>http://www.instagram.com/bbgym_gimpo</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,15 +797,19 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w480r7</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -809,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>115</v>
+        <v>704</v>
       </c>
       <c r="Q4" t="n">
-        <v>437</v>
+        <v>795</v>
       </c>
       <c r="R4" t="n">
-        <v>552</v>
+        <v>1499</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1075826288</t>
+          <t>37942639</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1075826288</t>
+          <t>https://m.place.naver.com/place/37942639</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -841,39 +853,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>포짐 헬스&amp;PT 김포 장기본점</t>
+          <t>인어스휘트니스 헬스 PT &amp; 필라테스 골프 김포점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pogym1@naver.com</t>
+          <t>inus-fitness09@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1397-5997</t>
+          <t>0507-1312-8337</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 김포시 청송로 8 석권에듀프라자 501, 505호</t>
+          <t>경기 김포시 김포한강4로 113 신한프라자 10층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/pogym1</t>
+          <t>https://inushnl.com/layout/fitness/home.php?go=main&amp;</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -888,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w45d2f</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -903,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>586</v>
+        <v>1410</v>
       </c>
       <c r="Q5" t="n">
-        <v>607</v>
+        <v>784</v>
       </c>
       <c r="R5" t="n">
-        <v>1193</v>
+        <v>2194</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1315590765</t>
+          <t>1901435715</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1315590765</t>
+          <t>https://m.place.naver.com/place/1901435715</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -935,34 +951,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>포짐 헬스&amp;PT 풍무점</t>
+          <t>오픈짐 구래점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pogym2@naver.com</t>
+          <t>opengym@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1366-6455</t>
+          <t>0507-1396-0969</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 김포시 풍무로 128 웰라움퍼펙트시티 4층 401-405호</t>
+          <t>경기 김포시 김포한강8로 378 9층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/po_gym_2/</t>
+          <t>https://www.instagram.com/opengym_gurae</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -982,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4dbcj</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -997,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>597</v>
+        <v>1931</v>
       </c>
       <c r="Q6" t="n">
-        <v>645</v>
+        <v>230</v>
       </c>
       <c r="R6" t="n">
-        <v>1242</v>
+        <v>2161</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1361528965</t>
+          <t>1547695145</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1361528965</t>
+          <t>https://m.place.naver.com/place/1547695145</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1029,34 +1049,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>피트니스벨 여성전용 헬스 PT 구래동점</t>
+          <t>웰리브라운지 PT 필라테스 구래동점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>fitnessbelle@naver.com</t>
+          <t>withusfitness@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1338-1365</t>
+          <t>0507-1368-7369</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 김포시 김포한강9로 79 연세프라자5차 6층</t>
+          <t>경기 김포시 김포한강8로 386 1001-1004호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitnessbelle</t>
+          <t>https://www.instagram.com/welliv.lounge</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1071,15 +1091,19 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w7j3ezw</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1091,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>765</v>
+        <v>489</v>
       </c>
       <c r="Q7" t="n">
-        <v>331</v>
+        <v>621</v>
       </c>
       <c r="R7" t="n">
-        <v>1096</v>
+        <v>1110</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1420264352</t>
+          <t>1523485481</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1420264352</t>
+          <t>https://m.place.naver.com/place/1523485481</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1123,39 +1147,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>포짐 헬스&amp;PT 운양점</t>
+          <t>짐원휘트니스 구래2호점 헬스PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>pogym3@naver.com</t>
+          <t>gymonelab@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1314-6455</t>
+          <t>0507-1438-9680</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 김포시 김포한강11로 218 굿프라임스포츠몰 506~509호</t>
+          <t>경기 김포시 김포한강8로 400 홍은프라자 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pogym3</t>
+          <t>http://gymone.kr</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1170,28 +1194,32 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w414b2</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>191</v>
+        <v>1023</v>
       </c>
       <c r="Q8" t="n">
-        <v>185</v>
+        <v>347</v>
       </c>
       <c r="R8" t="n">
-        <v>376</v>
+        <v>1370</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2089199431</t>
+          <t>1143886551</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2089199431</t>
+          <t>https://m.place.naver.com/place/1143886551</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1217,34 +1245,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>데이온휘트니스 헬스&amp;PT 풍무 2호점</t>
+          <t>브이짐 헬스&amp;PT 풍무점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>day_on22@naver.com</t>
+          <t>lki666@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1466-1467</t>
+          <t>0507-1433-9679</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 김포시 풍무로 8 5층</t>
+          <t>경기 김포시 풍무로 20 스타프라자</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/day_on22</t>
+          <t>https://blog.naver.com/lki666</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>311</v>
+        <v>115</v>
       </c>
       <c r="Q9" t="n">
-        <v>1243</v>
+        <v>440</v>
       </c>
       <c r="R9" t="n">
-        <v>1554</v>
+        <v>555</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1731905943</t>
+          <t>1075826288</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1731905943</t>
+          <t>https://m.place.naver.com/place/1075826288</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1311,44 +1339,44 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>제온휘트니스 헬스&amp;PT 풍무점</t>
+          <t>헨트 피트니스 헬스&amp;PT 풍무점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>doeunhee10@naver.com</t>
+          <t>hentfitness@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1432-8070</t>
+          <t>0507-1310-2603</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 김포시 풍무로 104 윤슬프라자 4층 401, 402, 403호 제온휘트니스</t>
+          <t>경기 김포시 풍무로 112 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://open.kakao.com/o/sO2iZ5Bh</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1358,28 +1386,32 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4spk6</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>498</v>
+        <v>204</v>
       </c>
       <c r="Q10" t="n">
-        <v>780</v>
+        <v>703</v>
       </c>
       <c r="R10" t="n">
-        <v>1278</v>
+        <v>907</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1969341019</t>
+          <t>1735469913</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1969341019</t>
+          <t>https://m.place.naver.com/place/1735469913</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1405,39 +1437,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>청년피티 풍무점 헬스PT</t>
+          <t>MUV 무브헬스&amp;PT 구래점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>joguboy@naver.com</t>
+          <t>mayhappy1120@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1377-3455</t>
+          <t>0507-1353-3253</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 김포시 유현로237번길 80 2층 청년피티</t>
+          <t>경기 김포시 김포한강4로 521 7층 무브헬스</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cnptoffical.qshop.ai/</t>
+          <t>https://blog.naver.com/mayhappy1120</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1447,15 +1479,19 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w2ty2ck</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1467,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>482</v>
+        <v>93</v>
       </c>
       <c r="Q11" t="n">
-        <v>220</v>
+        <v>24</v>
       </c>
       <c r="R11" t="n">
-        <v>702</v>
+        <v>117</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,12 +1518,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1468505293</t>
+          <t>2026337298</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1468505293</t>
+          <t>https://m.place.naver.com/place/2026337298</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1499,34 +1535,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>여성전용 피트니스지금 헬스&amp;PT 풍무점</t>
+          <t>지오짐24시</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>pakorea95@naver.com</t>
+          <t>giogym24hour@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1409-4879</t>
+          <t>0507-1480-3047</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 김포시 풍무로146번길 26 5층 501호</t>
+          <t>경기 김포시 양촌읍 양곡2로 50 7층 지오짐24시</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pakorea95/223610220210</t>
+          <t>https://blog.naver.com/giogym24hour</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1546,10 +1582,14 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5zkre</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1561,13 +1601,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>144</v>
+        <v>385</v>
       </c>
       <c r="Q12" t="n">
-        <v>286</v>
+        <v>540</v>
       </c>
       <c r="R12" t="n">
-        <v>430</v>
+        <v>925</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,861 +1616,15 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1997310621</t>
+          <t>1357314862</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1997310621</t>
+          <t>https://m.place.naver.com/place/1357314862</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>매스짐 헬스&amp;PT 풍무점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>fmgym123@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1321-7391</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>경기도 김포시 유현로238번길 11 드림프라자 8층 매스짐</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/fmgym123</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>136</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>530</v>
-      </c>
-      <c r="R13" t="n">
-        <v>666</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1933746777</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1933746777</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>위너핏 마송점</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>boos66@naver.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1319-4816</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>경기도 김포시 통진읍 마송1로84번길 53 7층</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/boos66</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>114</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>166</v>
-      </c>
-      <c r="R14" t="n">
-        <v>280</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>1043243355</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1043243355</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>오픈짐 구래점</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>opengym@naver.com</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0507-1396-0969</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>경기도 김포시 김포한강8로 378 9층</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/opengym_gurae</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>1931</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>230</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2161</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>1547695145</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1547695145</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>웰리브라운지 PT 필라테스 구래동점</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>withusfitness@naver.com</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0507-1368-7369</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>경기도 김포시 김포한강8로 386 1001-1004호</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/welliv.lounge</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>489</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>621</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1110</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1523485481</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1523485481</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>라이프블루 피트니스 구래점PT</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>bluegurae@naver.com</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0507-1357-2871</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>경기도 김포시 김포한강9로75번길 38 6층</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>https://booking.naver.com/booking/6/bizes/485614</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>654</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1288</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1942</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>1593392745</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1593392745</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>영자피트니스 김포구래점</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>yjfitness5@naver.com</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>031-986-5200</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>경기도 김포시 김포한강4로 525 5층 영자피트니스 김포구래</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>https://youtube.com/@영자피트니스김포</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>540</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>523</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1063</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>1491091700</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1491091700</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>라임 피트니스 PT 김포장기점</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>lime___fitness@naver.com</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0507-1381-7494</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>경기도 김포시 태장로 780 베네치아의 아침 3층</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/lime___fitness</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>480</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>488</v>
-      </c>
-      <c r="R19" t="n">
-        <v>968</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>1802881557</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1802881557</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>포워드 휘트니스 감정점</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>forward-fitness2@naver.com</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0507-1414-6704</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>경기도 김포시 중봉1로 17 4층</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/forward.fitness.02</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>340</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>575</v>
-      </c>
-      <c r="R20" t="n">
-        <v>915</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>1451785502</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1451785502</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>오픈짐 김포시청점</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>opengym@naver.com</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0507-1337-0969</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>경기도 김포시 김포대로 847 8층</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/opengym</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>1340</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>148</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1488</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>1077945140</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1077945140</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
         <is>
           <t>2026-04-14</t>
         </is>

--- a/naver-place-crawler/results_health/김포_헬스장.xlsx
+++ b/naver-place-crawler/results_health/김포_헬스장.xlsx
@@ -421,12 +421,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>라임 피트니스 PT 김포장기점</t>
+          <t>라운지 휘트니스 헬스&amp;PT&amp;GX&amp;스피닝&amp;필라 운양점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>lime___fitness@naver.com</t>
+          <t>lounge_fitness@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1381-7494</t>
+          <t>0507-1360-7495</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 김포시 태장로 780 베네치아의 아침 3층</t>
+          <t>경기 김포시 김포한강1로 230 9층 901~907, 922~925호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lime___fitness</t>
+          <t>https://blog.naver.com/lounge_fitness</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4hh9p</t>
+          <t>https://talk.naver.com/ct/w42s1j</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>480</v>
+        <v>304</v>
       </c>
       <c r="Q2" t="n">
-        <v>488</v>
+        <v>268</v>
       </c>
       <c r="R2" t="n">
-        <v>968</v>
+        <v>572</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1802881557</t>
+          <t>1798562504</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1802881557</t>
+          <t>https://m.place.naver.com/place/1798562504</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>포워드 휘트니스 감정점</t>
+          <t>라임 피트니스 PT 김포장기점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>forward-fitness2@naver.com</t>
+          <t>lime___fitness@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1414-6704</t>
+          <t>0507-1381-7494</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 김포시 중봉1로 17 4층</t>
+          <t>경기 김포시 태장로 780 베네치아의 아침 3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/forward.fitness.02</t>
+          <t>https://blog.naver.com/lime___fitness</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w936str</t>
+          <t>https://talk.naver.com/ct/w4hh9p</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>340</v>
+        <v>480</v>
       </c>
       <c r="Q3" t="n">
-        <v>576</v>
+        <v>492</v>
       </c>
       <c r="R3" t="n">
-        <v>916</v>
+        <v>972</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1451785502</t>
+          <t>1802881557</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1451785502</t>
+          <t>https://m.place.naver.com/place/1802881557</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>비비짐 김포점</t>
+          <t>포워드 휘트니스 감정점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bbgymgimpo@naver.com</t>
+          <t>forward-fitness2@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1402-5223</t>
+          <t>0507-1414-6704</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 김포시 사우중로 93 한빛프라자 7층</t>
+          <t>경기 김포시 중봉1로 17 4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/bbgym_gimpo</t>
+          <t>https://www.instagram.com/forward.fitness.02</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w480r7</t>
+          <t>https://talk.naver.com/ct/w936str</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>704</v>
+        <v>338</v>
       </c>
       <c r="Q4" t="n">
-        <v>795</v>
+        <v>585</v>
       </c>
       <c r="R4" t="n">
-        <v>1499</v>
+        <v>923</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>37942639</t>
+          <t>1451785502</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37942639</t>
+          <t>https://m.place.naver.com/place/1451785502</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -858,34 +858,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>인어스휘트니스 헬스 PT &amp; 필라테스 골프 김포점</t>
+          <t>오픈짐 구래점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>inus-fitness09@naver.com</t>
+          <t>opengym@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1312-8337</t>
+          <t>0507-1396-0969</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 김포시 김포한강4로 113 신한프라자 10층</t>
+          <t>경기 김포시 김포한강8로 378 9층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://inushnl.com/layout/fitness/home.php?go=main&amp;</t>
+          <t>https://www.instagram.com/opengym_gurae</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w45d2f</t>
+          <t>https://talk.naver.com/ct/w4dbcj</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1410</v>
+        <v>1936</v>
       </c>
       <c r="Q5" t="n">
-        <v>784</v>
+        <v>231</v>
       </c>
       <c r="R5" t="n">
-        <v>2194</v>
+        <v>2167</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +934,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1901435715</t>
+          <t>1547695145</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1901435715</t>
+          <t>https://m.place.naver.com/place/1547695145</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -956,34 +956,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>오픈짐 구래점</t>
+          <t>인어스휘트니스 헬스 PT &amp; 필라테스 골프 김포점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>opengym@naver.com</t>
+          <t>inus-fitness09@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1396-0969</t>
+          <t>0507-1312-8337</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 김포시 김포한강8로 378 9층</t>
+          <t>경기 김포시 김포한강4로 113 신한프라자 10층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/opengym_gurae</t>
+          <t>https://inushnl.com/layout/fitness/home.php?go=main&amp;</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4dbcj</t>
+          <t>https://talk.naver.com/ct/w45d2f</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1931</v>
+        <v>1411</v>
       </c>
       <c r="Q6" t="n">
-        <v>230</v>
+        <v>797</v>
       </c>
       <c r="R6" t="n">
-        <v>2161</v>
+        <v>2208</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1547695145</t>
+          <t>1901435715</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1547695145</t>
+          <t>https://m.place.naver.com/place/1901435715</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1054,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>웰리브라운지 PT 필라테스 구래동점</t>
+          <t>브이짐 헬스&amp;PT 풍무점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>withusfitness@naver.com</t>
+          <t>lki666@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1368-7369</t>
+          <t>0507-1433-9679</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 김포시 김포한강8로 386 1001-1004호</t>
+          <t>경기 김포시 풍무로 20 스타프라자</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/welliv.lounge</t>
+          <t>https://blog.naver.com/lki666</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,19 +1091,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w7j3ezw</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1115,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>489</v>
+        <v>115</v>
       </c>
       <c r="Q7" t="n">
-        <v>621</v>
+        <v>463</v>
       </c>
       <c r="R7" t="n">
-        <v>1110</v>
+        <v>578</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1126,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1523485481</t>
+          <t>1075826288</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1523485481</t>
+          <t>https://m.place.naver.com/place/1075826288</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1152,34 +1148,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>짐원휘트니스 구래2호점 헬스PT</t>
+          <t>웰리브라운지 PT 필라테스 구래동점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gymonelab@naver.com</t>
+          <t>withusfitness@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1438-9680</t>
+          <t>0507-1368-7369</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 김포시 김포한강8로 400 홍은프라자 4층</t>
+          <t>경기 김포시 김포한강8로 386 1001-1004호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://gymone.kr</t>
+          <t>https://www.instagram.com/welliv.lounge</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1189,7 +1185,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1199,12 +1195,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w414b2</t>
+          <t>https://talk.naver.com/ct/w7j3ezw</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1213,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1023</v>
+        <v>493</v>
       </c>
       <c r="Q8" t="n">
-        <v>347</v>
+        <v>634</v>
       </c>
       <c r="R8" t="n">
-        <v>1370</v>
+        <v>1127</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,17 +1224,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1143886551</t>
+          <t>1523485481</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1143886551</t>
+          <t>https://m.place.naver.com/place/1523485481</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1246,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>브이짐 헬스&amp;PT 풍무점</t>
+          <t>포짐 헬스&amp;PT 운양점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>lki666@naver.com</t>
+          <t>pogym3@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1433-9679</t>
+          <t>0507-1314-6455</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 김포시 풍무로 20 스타프라자</t>
+          <t>경기 김포시 김포한강11로 218 굿프라임스포츠몰 506~509호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lki666</t>
+          <t>https://blog.naver.com/pogym3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1292,10 +1288,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w8gabbl</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1303,17 +1303,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>115</v>
+        <v>204</v>
       </c>
       <c r="Q9" t="n">
-        <v>440</v>
+        <v>205</v>
       </c>
       <c r="R9" t="n">
-        <v>555</v>
+        <v>409</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,51 +1322,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1075826288</t>
+          <t>2089199431</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1075826288</t>
+          <t>https://m.place.naver.com/place/2089199431</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>헨트 피트니스 헬스&amp;PT 풍무점</t>
+          <t>엑스짐 헬스 PT 김포장기동점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>hentfitness@naver.com</t>
+          <t>cltnzz6736@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1310-2603</t>
+          <t>0507-1327-6736</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 김포시 풍무로 112 4층</t>
+          <t>경기 김포시 김포한강4로 129 하나프라자 7층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sO2iZ5Bh</t>
+          <t>https://zhenghwun91.wixsite.com/xgym</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4spk6</t>
+          <t>https://talk.naver.com/ct/w497xw</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="Q10" t="n">
-        <v>703</v>
+        <v>186</v>
       </c>
       <c r="R10" t="n">
-        <v>907</v>
+        <v>410</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,17 +1420,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1735469913</t>
+          <t>1567234519</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1735469913</t>
+          <t>https://m.place.naver.com/place/1567234519</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1442,29 +1442,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MUV 무브헬스&amp;PT 구래점</t>
+          <t>헨트 피트니스 헬스&amp;PT 풍무점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mayhappy1120@naver.com</t>
+          <t>hentfitness@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1353-3253</t>
+          <t>0507-1310-2603</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 김포시 김포한강4로 521 7층 무브헬스</t>
+          <t>경기 김포시 풍무로 112 4층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mayhappy1120</t>
+          <t>https://open.kakao.com/o/sO2iZ5Bh</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w2ty2ck</t>
+          <t>https://talk.naver.com/ct/w4spk6</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1503,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>93</v>
+        <v>203</v>
       </c>
       <c r="Q11" t="n">
-        <v>24</v>
+        <v>713</v>
       </c>
       <c r="R11" t="n">
-        <v>117</v>
+        <v>916</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,51 +1518,51 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026337298</t>
+          <t>1735469913</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2026337298</t>
+          <t>https://m.place.naver.com/place/1735469913</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>지오짐24시</t>
+          <t>모멘핏 재활PT 장기점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>giogym24hour@naver.com</t>
+          <t>dailyfitmemo@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1480-3047</t>
+          <t>0507-1338-0549</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기 김포시 양촌읍 양곡2로 50 7층 지오짐24시</t>
+          <t>경기 김포시 김포한강3로237번길 10 1동 2층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/giogym24hour</t>
+          <t>https://www.instagram.com/momentfit_janggi</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5zkre</t>
+          <t>https://talk.naver.com/ct/wgsn8pz</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1601,13 +1601,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>385</v>
+        <v>14</v>
       </c>
       <c r="Q12" t="n">
-        <v>540</v>
+        <v>20</v>
       </c>
       <c r="R12" t="n">
-        <v>925</v>
+        <v>34</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1616,17 +1616,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1357314862</t>
+          <t>2096364009</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1357314862</t>
+          <t>https://m.place.naver.com/place/2096364009</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/김포_헬스장.xlsx
+++ b/naver-place-crawler/results_health/김포_헬스장.xlsx
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -581,12 +581,12 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 김포시 김포한강1로 230 9층 901~907, 922~925호</t>
+          <t>경기도 김포시 김포한강1로 230 9층 901~907, 922~925호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lounge_fitness</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lime___fitness</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -726,10 +726,10 @@
         <v>480</v>
       </c>
       <c r="Q3" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="R3" t="n">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/forward.fitness.02</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -824,10 +824,10 @@
         <v>338</v>
       </c>
       <c r="Q4" t="n">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="R4" t="n">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/opengym_gurae</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="Q5" t="n">
         <v>231</v>
       </c>
       <c r="R5" t="n">
-        <v>2167</v>
+        <v>2168</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="Q6" t="n">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="R6" t="n">
-        <v>2208</v>
+        <v>2210</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lki666</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Q7" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="R7" t="n">
         <v>578</v>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/welliv.lounge</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1212,10 +1212,10 @@
         <v>493</v>
       </c>
       <c r="Q8" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="R8" t="n">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1246,34 +1246,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>포짐 헬스&amp;PT 운양점</t>
+          <t>청년피티 풍무점 헬스PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>pogym3@naver.com</t>
+          <t>joguboy@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1314-6455</t>
+          <t>0507-1377-3455</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 김포시 김포한강11로 218 굿프라임스포츠몰 506~509호</t>
+          <t>경기 김포시 유현로237번길 80 2층 청년피티</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pogym3</t>
+          <t>https://cnptoffical.qshop.ai/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w8gabbl</t>
+          <t>https://talk.naver.com/ct/w4tdc6</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>204</v>
+        <v>486</v>
       </c>
       <c r="Q9" t="n">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="R9" t="n">
-        <v>409</v>
+        <v>712</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,17 +1322,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2089199431</t>
+          <t>1468505293</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2089199431</t>
+          <t>https://m.place.naver.com/place/1468505293</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1430,41 +1430,41 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>헨트 피트니스 헬스&amp;PT 풍무점</t>
+          <t>모멘핏 재활PT 장기점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>hentfitness@naver.com</t>
+          <t>dailyfitmemo@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1310-2603</t>
+          <t>0507-1338-0549</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 김포시 풍무로 112 4층</t>
+          <t>경기 김포시 김포한강3로237번길 10 1동 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sO2iZ5Bh</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4spk6</t>
+          <t>https://talk.naver.com/ct/wgsn8pz</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1503,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>203</v>
+        <v>14</v>
       </c>
       <c r="Q11" t="n">
-        <v>713</v>
+        <v>20</v>
       </c>
       <c r="R11" t="n">
-        <v>916</v>
+        <v>34</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,51 +1518,51 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1735469913</t>
+          <t>2096364009</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1735469913</t>
+          <t>https://m.place.naver.com/place/2096364009</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>모멘핏 재활PT 장기점</t>
+          <t>오늘도필라테스&amp;바레 김포구래점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dailyfitmemo@naver.com</t>
+          <t>todaypilatesgr@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1338-0549</t>
+          <t>0507-1332-9003</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기 김포시 김포한강3로237번길 10 1동 2층</t>
+          <t>경기 김포시 김포한강8로 410 10층 1002호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/momentfit_janggi</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wgsn8pz</t>
+          <t>https://talk.naver.com/ct/w41b9k</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1601,13 +1601,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>14</v>
+        <v>217</v>
       </c>
       <c r="Q12" t="n">
-        <v>20</v>
+        <v>310</v>
       </c>
       <c r="R12" t="n">
-        <v>34</v>
+        <v>527</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1616,17 +1616,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2096364009</t>
+          <t>1884797711</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2096364009</t>
+          <t>https://m.place.naver.com/place/1884797711</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/김포_헬스장.xlsx
+++ b/naver-place-crawler/results_health/김포_헬스장.xlsx
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -581,12 +581,12 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 김포시 김포한강1로 230 9층 901~907, 922~925호</t>
+          <t>경기 김포시 김포한강1로 230 9층 901~907, 922~925호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/lounge_fitness</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/lime___fitness</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/forward.fitness.02</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/opengym_gurae</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/lki666</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/welliv.lounge</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1339,49 +1339,45 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>엑스짐 헬스 PT 김포장기동점</t>
+          <t>휘트니스바로PT 고촌점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cltnzz6736@naver.com</t>
+          <t>fitnessbaro_2@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1327-6736</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 김포시 김포한강4로 129 하나프라자 7층</t>
+          <t>경기 김포시 고촌읍 태리로 293 3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://zhenghwun91.wixsite.com/xgym</t>
+          <t>https://smartstore.naver.com/fitnessbaro</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1391,12 +1387,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w497xw</t>
+          <t>https://talk.naver.com/ct/wajkmaq</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1405,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>224</v>
+        <v>102</v>
       </c>
       <c r="Q10" t="n">
-        <v>186</v>
+        <v>48</v>
       </c>
       <c r="R10" t="n">
-        <v>410</v>
+        <v>150</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,12 +1416,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1567234519</t>
+          <t>2065106460</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1567234519</t>
+          <t>https://m.place.naver.com/place/2065106460</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1464,7 +1460,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/momentfit_janggi</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1474,7 +1470,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1562,7 +1558,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/todaypilates.gr</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1572,7 +1568,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">

--- a/naver-place-crawler/results_health/김포_헬스장.xlsx
+++ b/naver-place-crawler/results_health/김포_헬스장.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -628,10 +628,10 @@
         <v>338</v>
       </c>
       <c r="Q2" t="n">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="R2" t="n">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -662,39 +662,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>지오짐24시</t>
+          <t>인어스휘트니스 헬스 PT &amp; 필라테스 골프 김포점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>giogym24hour@naver.com</t>
+          <t>inus-fitness09@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1480-3047</t>
+          <t>0507-1312-8337</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 김포시 양촌읍 양곡2로 50 7층 지오짐24시</t>
+          <t>경기 김포시 김포한강4로 113 신한프라자 10층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://inushnl.com/layout/fitness/home.php?go=main&amp;</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5zkre</t>
+          <t>https://talk.naver.com/ct/w45d2f</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>391</v>
+        <v>1411</v>
       </c>
       <c r="Q3" t="n">
-        <v>552</v>
+        <v>803</v>
       </c>
       <c r="R3" t="n">
-        <v>943</v>
+        <v>2214</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1357314862</t>
+          <t>1901435715</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1357314862</t>
+          <t>https://m.place.naver.com/place/1901435715</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -760,39 +760,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>인어스휘트니스 헬스 PT &amp; 필라테스 골프 김포점</t>
+          <t>오픈짐 구래점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>inus-fitness09@naver.com</t>
+          <t>opengym@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1312-8337</t>
+          <t>0507-1396-0969</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 김포시 김포한강4로 113 신한프라자 10층</t>
+          <t>경기 김포시 김포한강8로 378 9층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://inushnl.com/layout/fitness/home.php?go=main&amp;</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w45d2f</t>
+          <t>https://talk.naver.com/ct/w4dbcj</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1412</v>
+        <v>1938</v>
       </c>
       <c r="Q4" t="n">
-        <v>801</v>
+        <v>231</v>
       </c>
       <c r="R4" t="n">
-        <v>2213</v>
+        <v>2169</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1901435715</t>
+          <t>1547695145</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1901435715</t>
+          <t>https://m.place.naver.com/place/1547695145</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,39 +858,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>오픈짐 구래점</t>
+          <t>청년피티 풍무점 헬스PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>opengym@naver.com</t>
+          <t>joguboy@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1396-0969</t>
+          <t>0507-1377-3455</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 김포시 김포한강8로 378 9층</t>
+          <t>경기 김포시 유현로237번길 80 2층 청년피티</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://cnptoffical.qshop.ai/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4dbcj</t>
+          <t>https://talk.naver.com/ct/w4tdc6</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1938</v>
+        <v>486</v>
       </c>
       <c r="Q5" t="n">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="R5" t="n">
-        <v>2169</v>
+        <v>714</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1547695145</t>
+          <t>1468505293</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1547695145</t>
+          <t>https://m.place.naver.com/place/1468505293</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/lki666</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -988,12 +988,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1016,10 +1016,10 @@
         <v>114</v>
       </c>
       <c r="Q6" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="R6" t="n">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1050,39 +1050,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>청년피티 풍무점 헬스PT</t>
+          <t>피트니스벨 여성전용 헬스 PT 구래동점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>joguboy@naver.com</t>
+          <t>fitnessbelle@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1377-3455</t>
+          <t>0507-1338-1365</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 김포시 유현로237번길 80 2층 청년피티</t>
+          <t>경기 김포시 김포한강9로 79 연세프라자5차 6층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cnptoffical.qshop.ai/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4tdc6</t>
+          <t>https://talk.naver.com/ct/w4vlz3</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>486</v>
+        <v>783</v>
       </c>
       <c r="Q7" t="n">
-        <v>228</v>
+        <v>331</v>
       </c>
       <c r="R7" t="n">
-        <v>714</v>
+        <v>1114</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1468505293</t>
+          <t>1420264352</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1468505293</t>
+          <t>https://m.place.naver.com/place/1420264352</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1143,39 +1143,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>피트니스벨 여성전용 헬스 PT 구래동점</t>
+          <t>엑스짐 헬스 PT 김포장기동점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>fitnessbelle@naver.com</t>
+          <t>cltnzz6736@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1338-1365</t>
+          <t>0507-1327-6736</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 김포시 김포한강9로 79 연세프라자5차 6층</t>
+          <t>경기 김포시 김포한강4로 129 하나프라자 7층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://zhenghwun91.wixsite.com/xgym</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4vlz3</t>
+          <t>https://talk.naver.com/ct/w497xw</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>783</v>
+        <v>224</v>
       </c>
       <c r="Q8" t="n">
-        <v>331</v>
+        <v>186</v>
       </c>
       <c r="R8" t="n">
-        <v>1114</v>
+        <v>410</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1420264352</t>
+          <t>1567234519</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1420264352</t>
+          <t>https://m.place.naver.com/place/1567234519</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1246,24 +1246,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>라운지 휘트니스 헬스&amp;PT&amp;GX&amp;스피닝&amp;필라 운양점</t>
+          <t>헨트 피트니스 헬스&amp;PT 풍무점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>lounge_fitness@naver.com</t>
+          <t>sang_2-@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1360-7495</t>
+          <t>0507-1310-2603</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 김포시 김포한강1로 230 9층 901~907, 922~925호</t>
+          <t>경기 김포시 풍무로 112 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w42s1j</t>
+          <t>https://talk.naver.com/ct/w4spk6</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>304</v>
+        <v>204</v>
       </c>
       <c r="Q9" t="n">
-        <v>269</v>
+        <v>715</v>
       </c>
       <c r="R9" t="n">
-        <v>573</v>
+        <v>919</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1798562504</t>
+          <t>1735469913</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1798562504</t>
+          <t>https://m.place.naver.com/place/1735469913</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1344,24 +1344,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>라운지휘트니스 헬스&amp;PT 구래점</t>
+          <t>MUV 무브헬스&amp;PT 구래점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>lounge_fitness2@naver.com</t>
+          <t>mayhappy1120@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1314-9498</t>
+          <t>0507-1353-3253</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 김포시 김포한강8로 304 3층 라운지 휘트니스 구래점</t>
+          <t>경기 김포시 김포한강4로 521 7층 MUV 무브헬스&amp;PT 구래점</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc359u9</t>
+          <t>https://talk.naver.com/ct/w2ty2ck</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>314</v>
+        <v>93</v>
       </c>
       <c r="Q10" t="n">
-        <v>166</v>
+        <v>23</v>
       </c>
       <c r="R10" t="n">
-        <v>480</v>
+        <v>116</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1129008408</t>
+          <t>2026337298</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1129008408</t>
+          <t>https://m.place.naver.com/place/2026337298</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1499,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q11" t="n">
         <v>48</v>
       </c>
       <c r="R11" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1536,24 +1536,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MUV 무브헬스&amp;PT 구래점</t>
+          <t>지오짐24시</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>mayhappy1120@naver.com</t>
+          <t>giogym24hour@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1353-3253</t>
+          <t>0507-1480-3047</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기 김포시 김포한강4로 521 7층 MUV 무브헬스&amp;PT 구래점</t>
+          <t>경기 김포시 양촌읍 양곡2로 50 7층 지오짐24시</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w2ty2ck</t>
+          <t>https://talk.naver.com/ct/w5zkre</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1597,13 +1597,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>92</v>
+        <v>391</v>
       </c>
       <c r="Q12" t="n">
-        <v>23</v>
+        <v>552</v>
       </c>
       <c r="R12" t="n">
-        <v>115</v>
+        <v>943</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1612,15 +1612,113 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026337298</t>
+          <t>1357314862</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2026337298</t>
+          <t>https://m.place.naver.com/place/1357314862</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>STA PT 김포구래점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>sta_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1492-0190</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>경기 김포시 김포한강8로 410 9층 STA PT</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4oqls</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>123</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>171</v>
+      </c>
+      <c r="R13" t="n">
+        <v>294</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1129851786</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1129851786</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>

--- a/naver-place-crawler/results_health/김포_헬스장.xlsx
+++ b/naver-place-crawler/results_health/김포_헬스장.xlsx
@@ -421,12 +421,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>포워드 휘트니스 감정점</t>
+          <t>라운지 휘트니스 헬스&amp;PT&amp;GX&amp;스피닝&amp;필라 운양점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>forward-fitness2@naver.com</t>
+          <t>lounge_fitness@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1414-6704</t>
+          <t>0507-1360-7495</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 김포시 중봉1로 17 4층</t>
+          <t>경기도 김포시 김포한강1로 230 9층 901~907, 922~925호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/lounge_fitness</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,24 +596,20 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w936str</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>338</v>
+        <v>304</v>
       </c>
       <c r="Q2" t="n">
-        <v>589</v>
+        <v>270</v>
       </c>
       <c r="R2" t="n">
-        <v>927</v>
+        <v>574</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1451785502</t>
+          <t>1798562504</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1451785502</t>
+          <t>https://m.place.naver.com/place/1798562504</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -662,34 +658,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>인어스휘트니스 헬스 PT &amp; 필라테스 골프 김포점</t>
+          <t>라임 피트니스 PT 김포장기점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>inus-fitness09@naver.com</t>
+          <t>lime___fitness@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1312-8337</t>
+          <t>0507-1381-7494</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 김포시 김포한강4로 113 신한프라자 10층</t>
+          <t>경기 김포시 태장로 780 베네치아의 아침 3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://inushnl.com/layout/fitness/home.php?go=main&amp;</t>
+          <t>https://blog.naver.com/lime___fitness</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -699,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -709,7 +705,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w45d2f</t>
+          <t>https://talk.naver.com/ct/w4hh9p</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1411</v>
+        <v>480</v>
       </c>
       <c r="Q3" t="n">
-        <v>803</v>
+        <v>494</v>
       </c>
       <c r="R3" t="n">
-        <v>2214</v>
+        <v>974</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +734,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1901435715</t>
+          <t>1802881557</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1901435715</t>
+          <t>https://m.place.naver.com/place/1802881557</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -760,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>오픈짐 구래점</t>
+          <t>포워드 휘트니스 감정점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>opengym@naver.com</t>
+          <t>forward-fitness2@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1396-0969</t>
+          <t>0507-1414-6704</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 김포시 김포한강8로 378 9층</t>
+          <t>경기 김포시 중봉1로 17 4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/forward.fitness.02</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,7 +788,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -807,7 +803,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4dbcj</t>
+          <t>https://talk.naver.com/ct/w936str</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1938</v>
+        <v>338</v>
       </c>
       <c r="Q4" t="n">
-        <v>231</v>
+        <v>590</v>
       </c>
       <c r="R4" t="n">
-        <v>2169</v>
+        <v>928</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +832,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1547695145</t>
+          <t>1451785502</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1547695145</t>
+          <t>https://m.place.naver.com/place/1451785502</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -858,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>청년피티 풍무점 헬스PT</t>
+          <t>인어스휘트니스 헬스 PT &amp; 필라테스 골프 김포점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>joguboy@naver.com</t>
+          <t>inus-fitness09@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1377-3455</t>
+          <t>0507-1312-8337</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 김포시 유현로237번길 80 2층 청년피티</t>
+          <t>경기 김포시 김포한강4로 113 신한프라자 10층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cnptoffical.qshop.ai/</t>
+          <t>https://inushnl.com/layout/fitness/home.php?go=main&amp;</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -905,7 +901,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4tdc6</t>
+          <t>https://talk.naver.com/ct/w45d2f</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>486</v>
+        <v>1411</v>
       </c>
       <c r="Q5" t="n">
-        <v>228</v>
+        <v>804</v>
       </c>
       <c r="R5" t="n">
-        <v>714</v>
+        <v>2215</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +930,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1468505293</t>
+          <t>1901435715</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1468505293</t>
+          <t>https://m.place.naver.com/place/1901435715</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -956,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>브이짐 헬스&amp;PT 풍무점</t>
+          <t>오픈짐 구래점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>lki666@naver.com</t>
+          <t>opengym@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1433-9679</t>
+          <t>0507-1396-0969</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 김포시 풍무로 20 스타프라자</t>
+          <t>경기 김포시 김포한강8로 378 9층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lki666</t>
+          <t>https://www.instagram.com/opengym_gurae</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,15 +989,19 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4dbcj</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>114</v>
+        <v>1938</v>
       </c>
       <c r="Q6" t="n">
-        <v>470</v>
+        <v>231</v>
       </c>
       <c r="R6" t="n">
-        <v>584</v>
+        <v>2169</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,17 +1028,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1075826288</t>
+          <t>1547695145</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1075826288</t>
+          <t>https://m.place.naver.com/place/1547695145</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1050,39 +1050,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>피트니스벨 여성전용 헬스 PT 구래동점</t>
+          <t>청년피티 풍무점 헬스PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>fitnessbelle@naver.com</t>
+          <t>joguboy@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1338-1365</t>
+          <t>0507-1377-3455</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 김포시 김포한강9로 79 연세프라자5차 6층</t>
+          <t>경기 김포시 유현로237번길 80 2층 청년피티</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://cnptoffical.qshop.ai/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4vlz3</t>
+          <t>https://talk.naver.com/ct/w4tdc6</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>783</v>
+        <v>486</v>
       </c>
       <c r="Q7" t="n">
-        <v>331</v>
+        <v>228</v>
       </c>
       <c r="R7" t="n">
-        <v>1114</v>
+        <v>714</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,61 +1126,61 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1420264352</t>
+          <t>1468505293</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1420264352</t>
+          <t>https://m.place.naver.com/place/1468505293</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>엑스짐 헬스 PT 김포장기동점</t>
+          <t>브이짐 헬스&amp;PT 풍무점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cltnzz6736@naver.com</t>
+          <t>lki666@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1327-6736</t>
+          <t>0507-1433-9679</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 김포시 김포한강4로 129 하나프라자 7층</t>
+          <t>경기 김포시 풍무로 20 스타프라자</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://zhenghwun91.wixsite.com/xgym</t>
+          <t>https://blog.naver.com/lki666</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1190,17 +1190,13 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w497xw</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1209,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>224</v>
+        <v>114</v>
       </c>
       <c r="Q8" t="n">
-        <v>186</v>
+        <v>470</v>
       </c>
       <c r="R8" t="n">
-        <v>410</v>
+        <v>584</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,17 +1220,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1567234519</t>
+          <t>1075826288</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1567234519</t>
+          <t>https://m.place.naver.com/place/1075826288</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1246,29 +1242,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>헨트 피트니스 헬스&amp;PT 풍무점</t>
+          <t>피트니스벨 여성전용 헬스 PT 구래동점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sang_2-@naver.com</t>
+          <t>fitnessbelle@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1310-2603</t>
+          <t>0507-1338-1365</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 김포시 풍무로 112 4층</t>
+          <t>경기 김포시 김포한강9로 79 연세프라자5차 6층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/fitnessbelle</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1278,12 +1274,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1293,12 +1289,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4spk6</t>
+          <t>https://talk.naver.com/ct/w4vlz3</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1307,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>204</v>
+        <v>782</v>
       </c>
       <c r="Q9" t="n">
-        <v>715</v>
+        <v>331</v>
       </c>
       <c r="R9" t="n">
-        <v>919</v>
+        <v>1113</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,17 +1318,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1735469913</t>
+          <t>1420264352</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1735469913</t>
+          <t>https://m.place.naver.com/place/1420264352</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1344,29 +1340,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MUV 무브헬스&amp;PT 구래점</t>
+          <t>라운지휘트니스 헬스&amp;PT 구래점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mayhappy1120@naver.com</t>
+          <t>lounge_fitness2@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1353-3253</t>
+          <t>0507-1314-9498</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 김포시 김포한강4로 521 7층 MUV 무브헬스&amp;PT 구래점</t>
+          <t>경기 김포시 김포한강8로 304 3층 라운지 휘트니스 구래점</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/lounge__fitness2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1376,7 +1372,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1391,7 +1387,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w2ty2ck</t>
+          <t>https://talk.naver.com/ct/wc359u9</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>93</v>
+        <v>314</v>
       </c>
       <c r="Q10" t="n">
-        <v>23</v>
+        <v>166</v>
       </c>
       <c r="R10" t="n">
-        <v>116</v>
+        <v>480</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,17 +1416,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026337298</t>
+          <t>1129008408</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2026337298</t>
+          <t>https://m.place.naver.com/place/1129008408</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1456,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://smartstore.naver.com/fitnessbaro</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1470,7 +1466,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1524,41 +1520,41 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>지오짐24시</t>
+          <t>모멘핏 재활PT 장기점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>giogym24hour@naver.com</t>
+          <t>dailyfitmemo@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1480-3047</t>
+          <t>0507-1338-0549</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기 김포시 양촌읍 양곡2로 50 7층 지오짐24시</t>
+          <t>경기 김포시 김포한강3로237번길 10 1동 2층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/momentfit_janggi</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1568,7 +1564,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1583,7 +1579,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5zkre</t>
+          <t>https://talk.naver.com/ct/wgsn8pz</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1597,13 +1593,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>391</v>
+        <v>15</v>
       </c>
       <c r="Q12" t="n">
-        <v>552</v>
+        <v>20</v>
       </c>
       <c r="R12" t="n">
-        <v>943</v>
+        <v>35</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1612,51 +1608,51 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1357314862</t>
+          <t>2096364009</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1357314862</t>
+          <t>https://m.place.naver.com/place/2096364009</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>STA PT 김포구래점</t>
+          <t>오늘도필라테스&amp;바레 김포구래점</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sta_pt@naver.com</t>
+          <t>todaypilatesgr@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1492-0190</t>
+          <t>0507-1332-9003</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기 김포시 김포한강8로 410 9층 STA PT</t>
+          <t>경기 김포시 김포한강8로 410 10층 1002호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/todaypilates.gr</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1666,7 +1662,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1681,12 +1677,12 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4oqls</t>
+          <t>https://talk.naver.com/ct/w41b9k</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1695,13 +1691,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>123</v>
+        <v>217</v>
       </c>
       <c r="Q13" t="n">
-        <v>171</v>
+        <v>310</v>
       </c>
       <c r="R13" t="n">
-        <v>294</v>
+        <v>527</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1710,17 +1706,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1129851786</t>
+          <t>1884797711</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1129851786</t>
+          <t>https://m.place.naver.com/place/1884797711</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/김포_헬스장.xlsx
+++ b/naver-place-crawler/results_health/김포_헬스장.xlsx
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 김포시 김포한강1로 230 9층 901~907, 922~925호</t>
+          <t>경기 김포시 김포한강1로 230 9층 901~907, 922~925호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42s1j</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -820,10 +824,10 @@
         <v>338</v>
       </c>
       <c r="Q4" t="n">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="R4" t="n">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1340,29 +1344,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>라운지휘트니스 헬스&amp;PT 구래점</t>
+          <t>헨트 피트니스 헬스&amp;PT 풍무점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>lounge_fitness2@naver.com</t>
+          <t>hentfitness@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1314-9498</t>
+          <t>0507-1310-2603</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 김포시 김포한강8로 304 3층 라운지 휘트니스 구래점</t>
+          <t>경기 김포시 풍무로 112 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lounge__fitness2</t>
+          <t>https://open.kakao.com/o/sO2iZ5Bh</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1387,12 +1391,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc359u9</t>
+          <t>https://talk.naver.com/ct/w4spk6</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1401,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>314</v>
+        <v>204</v>
       </c>
       <c r="Q10" t="n">
-        <v>166</v>
+        <v>716</v>
       </c>
       <c r="R10" t="n">
-        <v>480</v>
+        <v>920</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1129008408</t>
+          <t>1735469913</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1129008408</t>
+          <t>https://m.place.naver.com/place/1735469913</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1438,25 +1442,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>휘트니스바로PT 고촌점</t>
+          <t>라운지휘트니스 헬스&amp;PT 구래점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>fitnessbaro_2@naver.com</t>
+          <t>lounge_fitness2@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1314-9498</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 김포시 고촌읍 태리로 293 3층</t>
+          <t>경기 김포시 김포한강8로 304 3층 라운지 휘트니스 구래점</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/fitnessbaro</t>
+          <t>https://www.instagram.com/lounge__fitness2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1481,7 +1489,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wajkmaq</t>
+          <t>https://talk.naver.com/ct/wc359u9</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1495,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>103</v>
+        <v>314</v>
       </c>
       <c r="Q11" t="n">
-        <v>48</v>
+        <v>166</v>
       </c>
       <c r="R11" t="n">
-        <v>151</v>
+        <v>480</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1510,12 +1518,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2065106460</t>
+          <t>1129008408</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2065106460</t>
+          <t>https://m.place.naver.com/place/1129008408</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
